--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125446722</v>
+        <v>125446710</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125446712</v>
+        <v>125446788</v>
       </c>
       <c r="B3" t="n">
-        <v>56423</v>
+        <v>56537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428692</v>
+        <v>428724</v>
       </c>
       <c r="R3" t="n">
-        <v>6218408</v>
+        <v>6218473</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125446779</v>
+        <v>125446722</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
+        <v>56525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R4" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446708</v>
+        <v>125446977</v>
       </c>
       <c r="B5" t="n">
-        <v>56404</v>
+        <v>77276</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,46 +1024,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>1342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428692</v>
+        <v>428846</v>
       </c>
       <c r="R5" t="n">
-        <v>6218408</v>
+        <v>6218527</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1086,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,8 +1100,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1119,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446799</v>
+        <v>125446779</v>
       </c>
       <c r="B6" t="n">
-        <v>56418</v>
+        <v>56525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1230,14 +1260,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446977</v>
+        <v>125446763</v>
       </c>
       <c r="B7" t="n">
-        <v>77146</v>
+        <v>56516</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1246,40 +1276,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1342</v>
+        <v>100015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428846</v>
+        <v>428724</v>
       </c>
       <c r="R7" t="n">
-        <v>6218527</v>
+        <v>6218473</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,12 +1344,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen bok.</t>
+          <t>Endast några enstaka ljudfiler över flera nätter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,39 +1358,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1371,14 +1376,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125446763</v>
+        <v>125446708</v>
       </c>
       <c r="B8" t="n">
-        <v>56402</v>
+        <v>56518</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1387,21 +1392,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R8" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1456,11 +1461,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Endast några enstaka ljudfiler över flera nätter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,7 +1490,7 @@
         <v>125446726</v>
       </c>
       <c r="B9" t="n">
-        <v>56425</v>
+        <v>56539</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446710</v>
+        <v>125446712</v>
       </c>
       <c r="B10" t="n">
-        <v>56418</v>
+        <v>56537</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125446788</v>
+        <v>125446799</v>
       </c>
       <c r="B11" t="n">
-        <v>56423</v>
+        <v>56532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446726</v>
+        <v>125446712</v>
       </c>
       <c r="B9" t="n">
-        <v>56539</v>
+        <v>56537</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,25 +1499,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446712</v>
+        <v>125446726</v>
       </c>
       <c r="B10" t="n">
-        <v>56537</v>
+        <v>56539</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125446710</v>
+        <v>125446977</v>
       </c>
       <c r="B2" t="n">
-        <v>56532</v>
+        <v>77276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>1342</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428692</v>
+        <v>428846</v>
       </c>
       <c r="R2" t="n">
-        <v>6218408</v>
+        <v>6218527</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +753,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,8 +767,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,7 +816,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125446788</v>
+        <v>125446712</v>
       </c>
       <c r="B3" t="n">
         <v>56537</v>
@@ -835,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R3" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -897,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125446722</v>
+        <v>125446710</v>
       </c>
       <c r="B4" t="n">
-        <v>56525</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1008,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446977</v>
+        <v>125446799</v>
       </c>
       <c r="B5" t="n">
-        <v>77276</v>
+        <v>56532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,44 +1050,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1342</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428846</v>
+        <v>428724</v>
       </c>
       <c r="R5" t="n">
-        <v>6218527</v>
+        <v>6218473</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1122,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,39 +1131,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446779</v>
+        <v>125446788</v>
       </c>
       <c r="B6" t="n">
-        <v>56525</v>
+        <v>56537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1260,14 +1260,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446763</v>
+        <v>125446726</v>
       </c>
       <c r="B7" t="n">
-        <v>56516</v>
+        <v>56539</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100015</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R7" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1345,11 +1345,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Endast några enstaka ljudfiler över flera nätter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125446708</v>
+        <v>125446779</v>
       </c>
       <c r="B8" t="n">
-        <v>56518</v>
+        <v>56525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428692</v>
+        <v>428724</v>
       </c>
       <c r="R8" t="n">
-        <v>6218408</v>
+        <v>6218473</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1487,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446712</v>
+        <v>125446722</v>
       </c>
       <c r="B9" t="n">
-        <v>56537</v>
+        <v>56525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446726</v>
+        <v>125446708</v>
       </c>
       <c r="B10" t="n">
-        <v>56539</v>
+        <v>56518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,32 +1704,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125446799</v>
+        <v>125446763</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>56516</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1796,6 +1791,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Endast några enstaka ljudfiler över flera nätter.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -675,56 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125446977</v>
+        <v>125446788</v>
       </c>
       <c r="B2" t="n">
-        <v>77276</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1342</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428846</v>
+        <v>428724</v>
       </c>
       <c r="R2" t="n">
-        <v>6218527</v>
+        <v>6218473</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +754,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,39 +763,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -816,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125446712</v>
+        <v>125446710</v>
       </c>
       <c r="B3" t="n">
-        <v>56537</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -927,32 +887,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125446710</v>
+        <v>125446763</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -976,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428692</v>
+        <v>428724</v>
       </c>
       <c r="R4" t="n">
-        <v>6218408</v>
+        <v>6218473</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1012,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Endast några enstaka ljudfiler över flera nätter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,62 +998,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446799</v>
+        <v>125446977</v>
       </c>
       <c r="B5" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>1342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428724</v>
+        <v>428846</v>
       </c>
       <c r="R5" t="n">
-        <v>6218473</v>
+        <v>6218527</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1071,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,8 +1085,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,15 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446788</v>
+        <v>125446712</v>
       </c>
       <c r="B6" t="n">
-        <v>56537</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R6" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1263,12 +1243,7 @@
         <v>125446726</v>
       </c>
       <c r="B7" t="n">
-        <v>56539</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,15 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125446779</v>
+        <v>125446722</v>
       </c>
       <c r="B8" t="n">
-        <v>56525</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R8" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1482,15 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446722</v>
+        <v>125446779</v>
       </c>
       <c r="B9" t="n">
-        <v>56525</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428692</v>
+        <v>428724</v>
       </c>
       <c r="R9" t="n">
-        <v>6218408</v>
+        <v>6218473</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1593,37 +1558,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446708</v>
+        <v>125446799</v>
       </c>
       <c r="B10" t="n">
-        <v>56518</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1642,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428692</v>
+        <v>428724</v>
       </c>
       <c r="R10" t="n">
-        <v>6218408</v>
+        <v>6218473</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1704,15 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125446763</v>
+        <v>125446708</v>
       </c>
       <c r="B11" t="n">
-        <v>56516</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R11" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1789,11 +1744,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Endast några enstaka ljudfiler över flera nätter.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446779</v>
+        <v>125446799</v>
       </c>
       <c r="B9" t="n">
-        <v>56526</v>
+        <v>56533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446799</v>
+        <v>125446779</v>
       </c>
       <c r="B10" t="n">
-        <v>56533</v>
+        <v>56526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -998,51 +998,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446977</v>
+        <v>125446712</v>
       </c>
       <c r="B5" t="n">
-        <v>77318</v>
+        <v>56538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1342</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428846</v>
+        <v>428692</v>
       </c>
       <c r="R5" t="n">
-        <v>6218527</v>
+        <v>6218408</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1077,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,39 +1086,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1134,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446712</v>
+        <v>125446726</v>
       </c>
       <c r="B6" t="n">
-        <v>56538</v>
+        <v>56540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1240,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446726</v>
+        <v>125446977</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
+        <v>77318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,46 +1221,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>1342</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428692</v>
+        <v>428846</v>
       </c>
       <c r="R7" t="n">
-        <v>6218408</v>
+        <v>6218527</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1283,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,8 +1297,39 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446799</v>
+        <v>125446779</v>
       </c>
       <c r="B9" t="n">
-        <v>56533</v>
+        <v>56526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446779</v>
+        <v>125446799</v>
       </c>
       <c r="B10" t="n">
-        <v>56526</v>
+        <v>56533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -998,57 +998,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446712</v>
+        <v>125446977</v>
       </c>
       <c r="B5" t="n">
-        <v>56538</v>
+        <v>77319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>1342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428692</v>
+        <v>428846</v>
       </c>
       <c r="R5" t="n">
-        <v>6218408</v>
+        <v>6218527</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,7 +1071,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,8 +1085,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1104,32 +1134,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446726</v>
+        <v>125446712</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
+        <v>56538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446977</v>
+        <v>125446726</v>
       </c>
       <c r="B7" t="n">
-        <v>77318</v>
+        <v>56540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,40 +1251,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1342</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428846</v>
+        <v>428692</v>
       </c>
       <c r="R7" t="n">
-        <v>6218527</v>
+        <v>6218408</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1319,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,39 +1328,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446779</v>
+        <v>125446799</v>
       </c>
       <c r="B9" t="n">
-        <v>56526</v>
+        <v>56533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446799</v>
+        <v>125446779</v>
       </c>
       <c r="B10" t="n">
-        <v>56533</v>
+        <v>56526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -998,51 +998,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446977</v>
+        <v>125446712</v>
       </c>
       <c r="B5" t="n">
-        <v>77319</v>
+        <v>56538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1342</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428846</v>
+        <v>428692</v>
       </c>
       <c r="R5" t="n">
-        <v>6218527</v>
+        <v>6218408</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1077,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,39 +1086,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1134,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446712</v>
+        <v>125446726</v>
       </c>
       <c r="B6" t="n">
-        <v>56538</v>
+        <v>56540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1240,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446726</v>
+        <v>125446977</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
+        <v>77323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,46 +1221,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>1342</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428692</v>
+        <v>428846</v>
       </c>
       <c r="R7" t="n">
-        <v>6218408</v>
+        <v>6218527</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1283,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,8 +1297,39 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446799</v>
+        <v>125446779</v>
       </c>
       <c r="B9" t="n">
-        <v>56533</v>
+        <v>56526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446779</v>
+        <v>125446799</v>
       </c>
       <c r="B10" t="n">
-        <v>56526</v>
+        <v>56533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -998,57 +998,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446712</v>
+        <v>125446977</v>
       </c>
       <c r="B5" t="n">
-        <v>56538</v>
+        <v>77323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>1342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428692</v>
+        <v>428846</v>
       </c>
       <c r="R5" t="n">
-        <v>6218408</v>
+        <v>6218527</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,7 +1071,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,8 +1085,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1104,32 +1134,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446726</v>
+        <v>125446712</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
+        <v>56538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446977</v>
+        <v>125446726</v>
       </c>
       <c r="B7" t="n">
-        <v>77323</v>
+        <v>56540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,40 +1251,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1342</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428846</v>
+        <v>428692</v>
       </c>
       <c r="R7" t="n">
-        <v>6218527</v>
+        <v>6218408</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1319,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,39 +1328,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -998,51 +998,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446977</v>
+        <v>125446712</v>
       </c>
       <c r="B5" t="n">
-        <v>77323</v>
+        <v>56538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1342</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428846</v>
+        <v>428692</v>
       </c>
       <c r="R5" t="n">
-        <v>6218527</v>
+        <v>6218408</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1077,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,39 +1086,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1134,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446712</v>
+        <v>125446726</v>
       </c>
       <c r="B6" t="n">
-        <v>56538</v>
+        <v>56540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1240,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446726</v>
+        <v>125446977</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
+        <v>77323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,46 +1221,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>1342</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428692</v>
+        <v>428846</v>
       </c>
       <c r="R7" t="n">
-        <v>6218408</v>
+        <v>6218527</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1283,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,8 +1297,39 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446779</v>
+        <v>125446799</v>
       </c>
       <c r="B9" t="n">
-        <v>56526</v>
+        <v>56533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446799</v>
+        <v>125446779</v>
       </c>
       <c r="B10" t="n">
-        <v>56533</v>
+        <v>56526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125446788</v>
       </c>
       <c r="B2" t="n">
-        <v>56538</v>
+        <v>56539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125446710</v>
       </c>
       <c r="B3" t="n">
-        <v>56533</v>
+        <v>56534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125446763</v>
       </c>
       <c r="B4" t="n">
-        <v>56517</v>
+        <v>56518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>125446712</v>
       </c>
       <c r="B5" t="n">
-        <v>56538</v>
+        <v>56539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>125446726</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
+        <v>56541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>125446977</v>
       </c>
       <c r="B7" t="n">
-        <v>77323</v>
+        <v>77324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>125446722</v>
       </c>
       <c r="B8" t="n">
-        <v>56526</v>
+        <v>56527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>125446799</v>
       </c>
       <c r="B9" t="n">
-        <v>56533</v>
+        <v>56534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>125446779</v>
       </c>
       <c r="B10" t="n">
-        <v>56526</v>
+        <v>56527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>125446708</v>
       </c>
       <c r="B11" t="n">
-        <v>56519</v>
+        <v>56520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125446788</v>
+        <v>125446977</v>
       </c>
       <c r="B2" t="n">
-        <v>56539</v>
+        <v>77726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>1342</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10, Sk</t>
+          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428724</v>
+        <v>428846</v>
       </c>
       <c r="R2" t="n">
-        <v>6218473</v>
+        <v>6218527</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +748,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På senvuxen bok.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,8 +762,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bokskog i ravin</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Senvuxen klenare bok</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica # Senvuxen klenare bok</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,27 +811,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125446710</v>
+        <v>125446763</v>
       </c>
       <c r="B3" t="n">
-        <v>56534</v>
+        <v>56814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428692</v>
+        <v>428724</v>
       </c>
       <c r="R3" t="n">
-        <v>6218408</v>
+        <v>6218473</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -861,6 +891,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Endast några enstaka ljudfiler över flera nätter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +922,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125446763</v>
+        <v>125446710</v>
       </c>
       <c r="B4" t="n">
-        <v>56518</v>
+        <v>56830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R4" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -967,11 +1002,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Endast några enstaka ljudfiler över flera nätter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125446712</v>
+        <v>125446799</v>
       </c>
       <c r="B5" t="n">
-        <v>56539</v>
+        <v>56830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428692</v>
+        <v>428724</v>
       </c>
       <c r="R5" t="n">
-        <v>6218408</v>
+        <v>6218473</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1104,32 +1134,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125446726</v>
+        <v>125446722</v>
       </c>
       <c r="B6" t="n">
-        <v>56541</v>
+        <v>56823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,51 +1240,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125446977</v>
+        <v>125446779</v>
       </c>
       <c r="B7" t="n">
-        <v>77324</v>
+        <v>56823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1342</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vedhygge 1:10 - Nyckelbiotop i ravin, Sk</t>
+          <t>Vedhygge 1:10, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428846</v>
+        <v>428724</v>
       </c>
       <c r="R7" t="n">
-        <v>6218527</v>
+        <v>6218473</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1319,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På senvuxen bok.</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,39 +1328,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bokskog i ravin</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Senvuxen klenare bok</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica # Senvuxen klenare bok</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125446722</v>
+        <v>125446712</v>
       </c>
       <c r="B8" t="n">
-        <v>56527</v>
+        <v>56835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125446799</v>
+        <v>125446788</v>
       </c>
       <c r="B9" t="n">
-        <v>56534</v>
+        <v>56835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125446779</v>
+        <v>125446708</v>
       </c>
       <c r="B10" t="n">
-        <v>56527</v>
+        <v>56816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428724</v>
+        <v>428692</v>
       </c>
       <c r="R10" t="n">
-        <v>6218473</v>
+        <v>6218408</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125446708</v>
+        <v>125446726</v>
       </c>
       <c r="B11" t="n">
-        <v>56520</v>
+        <v>56837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>

--- a/artfynd/A 14105-2024 artfynd.xlsx
+++ b/artfynd/A 14105-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446977</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446763</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446799</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446722</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446779</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446712</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446788</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,8 +1817,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125446726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>